--- a/InputData/ctrl-settings/FoICStCT/Fraction of Industry Category Subject to Carbon Tax.xlsx
+++ b/InputData/ctrl-settings/FoICStCT/Fraction of Industry Category Subject to Carbon Tax.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndonesiaEPS/Shared Documents/Updated Indonesia InputData files/ctrl-settings/FoICStCT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\ctrl-settings\FoICStCT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04AF025E-9A8C-4B05-AB94-CE2A83E97C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236E01D0-9B26-4445-AD28-A754B818823E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9AA6BDF2-7B91-4567-88A2-0D83F9E3E450}"/>
+    <workbookView xWindow="31935" yWindow="3675" windowWidth="19200" windowHeight="11205" activeTab="1" xr2:uid="{9AA6BDF2-7B91-4567-88A2-0D83F9E3E450}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -742,14 +742,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE5FEEC-01CE-4291-999E-35B30A1256CF}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -757,32 +757,32 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -798,109 +798,112 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AE28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AF28"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="46.28515625" customWidth="1"/>
-    <col min="2" max="3" width="28" customWidth="1"/>
+    <col min="1" max="1" width="46.26953125" customWidth="1"/>
+    <col min="2" max="4" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5">
+        <v>2020</v>
+      </c>
+      <c r="C1" s="5">
         <v>2021</v>
       </c>
-      <c r="C1" s="5">
+      <c r="D1" s="5">
         <v>2022</v>
       </c>
-      <c r="D1" s="5">
+      <c r="E1" s="5">
         <v>2023</v>
       </c>
-      <c r="E1" s="5">
+      <c r="F1" s="5">
         <v>2024</v>
       </c>
-      <c r="F1" s="5">
+      <c r="G1" s="5">
         <v>2025</v>
       </c>
-      <c r="G1" s="5">
+      <c r="H1" s="5">
         <v>2026</v>
       </c>
-      <c r="H1" s="5">
+      <c r="I1" s="5">
         <v>2027</v>
       </c>
-      <c r="I1" s="5">
+      <c r="J1" s="5">
         <v>2028</v>
       </c>
-      <c r="J1" s="5">
+      <c r="K1" s="5">
         <v>2029</v>
       </c>
-      <c r="K1" s="5">
+      <c r="L1" s="5">
         <v>2030</v>
       </c>
-      <c r="L1" s="5">
+      <c r="M1" s="5">
         <v>2031</v>
       </c>
-      <c r="M1" s="5">
+      <c r="N1" s="5">
         <v>2032</v>
       </c>
-      <c r="N1" s="5">
+      <c r="O1" s="5">
         <v>2033</v>
       </c>
-      <c r="O1" s="5">
+      <c r="P1" s="5">
         <v>2034</v>
       </c>
-      <c r="P1" s="5">
+      <c r="Q1" s="5">
         <v>2035</v>
       </c>
-      <c r="Q1" s="5">
+      <c r="R1" s="5">
         <v>2036</v>
       </c>
-      <c r="R1" s="5">
+      <c r="S1" s="5">
         <v>2037</v>
       </c>
-      <c r="S1" s="5">
+      <c r="T1" s="5">
         <v>2038</v>
       </c>
-      <c r="T1" s="5">
+      <c r="U1" s="5">
         <v>2039</v>
       </c>
-      <c r="U1" s="5">
+      <c r="V1" s="5">
         <v>2040</v>
       </c>
-      <c r="V1" s="5">
+      <c r="W1" s="5">
         <v>2041</v>
       </c>
-      <c r="W1" s="5">
+      <c r="X1" s="5">
         <v>2042</v>
       </c>
-      <c r="X1" s="5">
+      <c r="Y1" s="5">
         <v>2043</v>
       </c>
-      <c r="Y1" s="5">
+      <c r="Z1" s="5">
         <v>2044</v>
       </c>
-      <c r="Z1" s="5">
+      <c r="AA1" s="5">
         <v>2045</v>
       </c>
-      <c r="AA1" s="5">
+      <c r="AB1" s="5">
         <v>2046</v>
       </c>
-      <c r="AB1" s="5">
+      <c r="AC1" s="5">
         <v>2047</v>
       </c>
-      <c r="AC1" s="5">
+      <c r="AD1" s="5">
         <v>2048</v>
       </c>
-      <c r="AD1" s="5">
+      <c r="AE1" s="5">
         <v>2049</v>
       </c>
-      <c r="AE1" s="5">
+      <c r="AF1" s="5">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -994,8 +997,11 @@
       <c r="AE2" s="4">
         <v>0</v>
       </c>
+      <c r="AF2" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1089,8 +1095,11 @@
       <c r="AE3" s="4">
         <v>1</v>
       </c>
+      <c r="AF3" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1184,8 +1193,11 @@
       <c r="AE4" s="4">
         <v>1</v>
       </c>
+      <c r="AF4" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1279,8 +1291,11 @@
       <c r="AE5" s="4">
         <v>1</v>
       </c>
+      <c r="AF5" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1374,8 +1389,11 @@
       <c r="AE6" s="4">
         <v>1</v>
       </c>
+      <c r="AF6" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1469,8 +1487,11 @@
       <c r="AE7" s="4">
         <v>1</v>
       </c>
+      <c r="AF7" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1564,8 +1585,11 @@
       <c r="AE8" s="4">
         <v>1</v>
       </c>
+      <c r="AF8" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1659,8 +1683,11 @@
       <c r="AE9" s="4">
         <v>1</v>
       </c>
+      <c r="AF9" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1754,8 +1781,11 @@
       <c r="AE10" s="4">
         <v>1</v>
       </c>
+      <c r="AF10" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1849,8 +1879,11 @@
       <c r="AE11" s="4">
         <v>1</v>
       </c>
+      <c r="AF11" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1944,8 +1977,11 @@
       <c r="AE12" s="4">
         <v>1</v>
       </c>
+      <c r="AF12" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2039,8 +2075,11 @@
       <c r="AE13" s="4">
         <v>1</v>
       </c>
+      <c r="AF13" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2134,8 +2173,11 @@
       <c r="AE14" s="4">
         <v>1</v>
       </c>
+      <c r="AF14" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2229,8 +2271,11 @@
       <c r="AE15" s="4">
         <v>1</v>
       </c>
+      <c r="AF15" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2324,8 +2369,11 @@
       <c r="AE16" s="4">
         <v>1</v>
       </c>
+      <c r="AF16" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2419,8 +2467,11 @@
       <c r="AE17" s="4">
         <v>1</v>
       </c>
+      <c r="AF17" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2514,8 +2565,11 @@
       <c r="AE18" s="4">
         <v>1</v>
       </c>
+      <c r="AF18" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2609,8 +2663,11 @@
       <c r="AE19" s="4">
         <v>1</v>
       </c>
+      <c r="AF19" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2704,8 +2761,11 @@
       <c r="AE20" s="4">
         <v>1</v>
       </c>
+      <c r="AF20" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2799,8 +2859,11 @@
       <c r="AE21" s="4">
         <v>1</v>
       </c>
+      <c r="AF21" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -2894,8 +2957,11 @@
       <c r="AE22" s="4">
         <v>1</v>
       </c>
+      <c r="AF22" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -2989,8 +3055,11 @@
       <c r="AE23" s="4">
         <v>1</v>
       </c>
+      <c r="AF23" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -3084,8 +3153,11 @@
       <c r="AE24" s="4">
         <v>1</v>
       </c>
+      <c r="AF24" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -3179,8 +3251,11 @@
       <c r="AE25" s="4">
         <v>0</v>
       </c>
+      <c r="AF25" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -3274,10 +3349,14 @@
       <c r="AE26" s="4">
         <v>1</v>
       </c>
+      <c r="AF26" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3291,15 +3370,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
     <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
@@ -3443,6 +3513,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7ECB671A-177C-429C-93F8-0D867FD308C6}">
   <ds:schemaRefs>
@@ -3453,14 +3532,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A780E627-E488-47DF-91D7-45CBC8359817}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53AD15D6-DF9E-4F54-9AAC-BAA9575FE69E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3476,4 +3547,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A780E627-E488-47DF-91D7-45CBC8359817}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>